--- a/output/StructureDefinition-PatientCreationDate.xlsx
+++ b/output/StructureDefinition-PatientCreationDate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T14:29:25+02:00</t>
+    <t>2026-10-14T17:02:42+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-PatientCreationDate.xlsx
+++ b/output/StructureDefinition-PatientCreationDate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T17:02:42+02:00</t>
+    <t>2026-10-15T08:29:54+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
